--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136365574</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136365595</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136356261</v>
       </c>
       <c r="B7" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
